--- a/data/trending_integrated_20260907_13.xlsx
+++ b/data/trending_integrated_20260907_13.xlsx
@@ -581,10 +581,10 @@
         <v>799</v>
       </c>
       <c r="F2" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
-        <v>1178</v>
+        <v>1223</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>775997663775</v>
+        <v>776552268475</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>-9000</v>
+        <v>1000</v>
       </c>
       <c r="S2" t="n">
         <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주포의 개입 및 물량 장악 언급. 거래량 동반 상승 및 3만원 돌파 기대감. 추가 상승 여력에 대한 긍정적 전망.</t>
+          <t>스카이랩스, 거래량 증가와 함께 급등 가능성 언급. '주포' 언급 등 시세 조종 관련 논란 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '상승 기대']</t>
+          <t>['거래량', '시세 조종', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10290</v>
+        <v>10220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.23%</t>
+          <t>+22.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>115959808690</v>
+        <v>118262341050</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,14 +711,14 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>70000</v>
+        <v>100000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-232000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>일론 머스크 및 두산에너빌리티 관련 뉴스와 연계된 가스터빈 테마 부각. 새로운 테마 형성 및 상한가 기대감. IBK 관련 매수세 언급.</t>
+          <t>삼미금속, 두산에너빌리티 및 일론 머스크 관련 가스터빈 테마 편입 가능성으로 급등. 신규 재료 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['가스터빈', '일론 머스크', '테마']</t>
+          <t>['가스터빈', '테마', '두산에너빌리티']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10040</v>
+        <v>9970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.74%</t>
+          <t>+21.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.44</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
         <v>1.58</v>
@@ -794,7 +794,7 @@
         <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>72233528755</v>
+        <v>75434428540</v>
       </c>
       <c r="P4" t="n">
         <v>22500</v>
@@ -803,23 +803,23 @@
         <v>4560</v>
       </c>
       <c r="R4" t="n">
-        <v>110000</v>
+        <v>152000</v>
       </c>
       <c r="S4" t="n">
         <v>-9000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주포 및 외인 프로그램 매수 등장 언급과 함께 AI 관련 뉴스 부각. 가격 변동성에 대한 불안감과 함께 매도/관망 의견 혼재.</t>
+          <t>매드업, AI 관련주로 부각되며 외국인·프로그램 매수세 유입. 매물대 소화 후 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '주포', '프로그램 매수']</t>
+          <t>['AI', '외국인 매수', '매물대']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51600</v>
+        <v>51800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.67%</t>
+          <t>+18.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="H5" t="n">
         <v>14.18</v>
@@ -886,7 +886,7 @@
         <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>139258734525</v>
+        <v>140581808925</v>
       </c>
       <c r="P5" t="n">
         <v>108900</v>
@@ -895,10 +895,10 @@
         <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>176000</v>
+        <v>156000</v>
       </c>
       <c r="S5" t="n">
-        <v>44000</v>
+        <v>-11000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18210</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.62%</t>
+          <t>+16.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" t="n">
         <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H6" t="n">
         <v>1.08</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>70797468275</v>
+        <v>74204682845</v>
       </c>
       <c r="P6" t="n">
         <v>34650</v>
@@ -987,23 +987,23 @@
         <v>6980</v>
       </c>
       <c r="R6" t="n">
-        <v>-21000</v>
+        <v>-36000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저평가 인식 및 18,500원 돌파에 대한 기대감. 반도체 주 강세 속 레메디 주가 흐름에 대한 의문 제기. 단타 거래에 유리하다는 의견.</t>
+          <t>레메디, 저평가된 기업으로 텐배거 기대감 존재. 저항대 소화 및 반도체 섹터 흐름에 따른 추가 상승 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '반도체', '단타']</t>
+          <t>['저평가', '텐배거', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3620</v>
+        <v>3605</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.87%</t>
+          <t>+10.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>182707647785</v>
+        <v>184414286932</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1079,14 +1079,14 @@
         <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>-25000</v>
+        <v>-840000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기적 가격 변동에 대한 언급과 함께 투자 주의 및 매도 권유. 특정 가격대에서의 매수/매도 공방이 관찰됨.</t>
+          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가격 변동', '투자 주의', '매도']</t>
+          <t>['투자주의', '탈모', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6460</v>
+        <v>86700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.43%</t>
+          <t>+9.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="G8" t="n">
-        <v>473</v>
+        <v>1054</v>
       </c>
       <c r="H8" t="n">
-        <v>1.61</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5850</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>6000</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>6550</v>
+        <v>87800</v>
       </c>
       <c r="M8" t="n">
-        <v>5940</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>2.31</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>14933843415</v>
+        <v>309901135300</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-14000</v>
+        <v>519000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
+          <t>두산에너빌리티, 일론 머스크 관련 뉴스 및 대규모 투자 발표로 인한 기대감 급증. 하반기 수주 전망 긍정적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['임상', '신약', '게임체인저']</t>
+          <t>['일론 머스크', '가스터빈', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86600</v>
+        <v>6370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.34%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>987</v>
+        <v>474</v>
       </c>
       <c r="H9" t="n">
-        <v>23.53</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>79200</v>
+        <v>5850</v>
       </c>
       <c r="K9" t="n">
-        <v>80200</v>
+        <v>6000</v>
       </c>
       <c r="L9" t="n">
-        <v>87800</v>
+        <v>6550</v>
       </c>
       <c r="M9" t="n">
-        <v>79000</v>
+        <v>5940</v>
       </c>
       <c r="N9" t="n">
-        <v>23.61</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>294644958200</v>
+        <v>15032602260</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>146000</v>
+        <v>-8000</v>
       </c>
       <c r="S9" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>일론 머스크 및 xAI 관련 뉴스와 연계된 긍정적 전망. 대규모 투자 및 6.3GW 가스복합 사업 관련 언급. 수급 개선 확인.</t>
+          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['일론 머스크', '가스복합', '수주']</t>
+          <t>['임상 2a', '폐암학회', '6500원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215000</v>
+        <v>1757000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.70%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>454</v>
+        <v>797</v>
       </c>
       <c r="F10" t="n">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="G10" t="n">
-        <v>1271</v>
+        <v>2633</v>
       </c>
       <c r="H10" t="n">
-        <v>29.46</v>
+        <v>50.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>201500</v>
+        <v>1647000</v>
       </c>
       <c r="K10" t="n">
-        <v>212500</v>
+        <v>1737000</v>
       </c>
       <c r="L10" t="n">
-        <v>225500</v>
+        <v>1758000</v>
       </c>
       <c r="M10" t="n">
-        <v>212500</v>
+        <v>1733000</v>
       </c>
       <c r="N10" t="n">
-        <v>29.51</v>
+        <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>302563989250</v>
+        <v>3441858171500</v>
       </c>
       <c r="P10" t="n">
-        <v>438000</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>74700</v>
+        <v>274000</v>
       </c>
       <c r="R10" t="n">
-        <v>353000</v>
+        <v>479000</v>
       </c>
       <c r="S10" t="n">
-        <v>124000</v>
+        <v>203000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
+          <t>SK하이닉스, 메모리 재고 감소 및 외국인·기관 매수세 증가로 인한 상승 추세 가속. 200달성 기대감 고조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2026', '모터 기술']</t>
+          <t>['메모리', '재고', '외국인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1753000</v>
+        <v>214500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.44%</t>
+          <t>+6.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>792</v>
+        <v>462</v>
       </c>
       <c r="F11" t="n">
-        <v>409</v>
+        <v>243</v>
       </c>
       <c r="G11" t="n">
-        <v>2456</v>
+        <v>1293</v>
       </c>
       <c r="H11" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K11" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L11" t="n">
-        <v>1754000</v>
+        <v>225500</v>
       </c>
       <c r="M11" t="n">
-        <v>1733000</v>
+        <v>212500</v>
       </c>
       <c r="N11" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>3308479719000</v>
+        <v>304727357250</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q11" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R11" t="n">
-        <v>330000</v>
+        <v>306000</v>
       </c>
       <c r="S11" t="n">
-        <v>138000</v>
+        <v>133000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>메모리 재고 감소 및 반등 기대감. 외국인, 기관의 쌍끌이 매수세 유입 확인. 180~200 내외 종가 및 상승 추세 가속 전망.</t>
+          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메모리 재고', '쌍끌이 매수', '상승 추세']</t>
+          <t>['로봇', 'CES 2026', '모터 기술']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8410</v>
+        <v>17850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>+5.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.72</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7950</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>8200</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>9210</v>
+        <v>17910</v>
       </c>
       <c r="M12" t="n">
-        <v>7980</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>93320537920</v>
+        <v>93629367575</v>
       </c>
       <c r="P12" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>149000</v>
+        <v>340000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17820</v>
+        <v>8360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5.76%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>10.4</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16850</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>16870</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>17860</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>16590</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>10.36</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>89682335950</v>
+        <v>93728011260</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>266000</v>
+        <v>26000</v>
       </c>
       <c r="S13" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>267000</v>
+        <v>267750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.50%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G14" t="n">
-        <v>1747</v>
+        <v>1877</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2251102102750</v>
+        <v>2349215087750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1723,14 +1723,14 @@
         <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>1189000</v>
+        <v>1309000</v>
       </c>
       <c r="S14" t="n">
-        <v>911000</v>
+        <v>1097000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입 감지. 재고 소진 및 3분기 영업이익 예상치에 대한 언급이 있으나, 정치적 언급과 함께 감정적 표현이 다수.</t>
+          <t>삼성전자, 반도체 재고 감소 및 HBM 가격 상승 기대감 형성. 그러나 정치적 언급과 불확실한 전망이 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['재고', '영업이익', '매수세']</t>
+          <t>['HBM', '재고', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>68312931285</v>
+        <v>68873394290</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,7 +1815,7 @@
         <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>317000</v>
+        <v>336000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1851,215 +1851,215 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22650</v>
+        <v>6750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K16" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L16" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M16" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N16" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>126743785400</v>
+        <v>11088297960</v>
       </c>
       <c r="P16" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q16" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R16" t="n">
-        <v>28000</v>
+        <v>-57000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16160</v>
+        <v>22550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>461</v>
+        <v>174</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K17" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L17" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M17" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O17" t="n">
-        <v>37677899785</v>
+        <v>127257326225</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R17" t="n">
-        <v>-21000</v>
+        <v>9000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 호남 반도체 산단 관련 기대감. 반도체 첫 삽 시 15만원 목표 언급 있으나, 구체적 근거는 부족.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '인프라']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30250</v>
+        <v>16120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="H18" t="n">
-        <v>48.95</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30200</v>
+        <v>16090</v>
       </c>
       <c r="K18" t="n">
-        <v>30350</v>
+        <v>16150</v>
       </c>
       <c r="L18" t="n">
-        <v>30900</v>
+        <v>16480</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>15830</v>
       </c>
       <c r="N18" t="n">
-        <v>24.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>68200986675</v>
+        <v>38839397945</v>
       </c>
       <c r="P18" t="n">
-        <v>31200</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>222000</v>
+        <v>31000</v>
       </c>
       <c r="S18" t="n">
-        <v>35000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['반도체', '산단', '주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6710</v>
+        <v>30250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H19" t="n">
-        <v>16.4</v>
+        <v>48.95</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6710</v>
+        <v>30200</v>
       </c>
       <c r="K19" t="n">
-        <v>6680</v>
+        <v>30350</v>
       </c>
       <c r="L19" t="n">
-        <v>7040</v>
+        <v>30900</v>
       </c>
       <c r="M19" t="n">
-        <v>6600</v>
+        <v>29900</v>
       </c>
       <c r="N19" t="n">
-        <v>15.55</v>
+        <v>24.02</v>
       </c>
       <c r="O19" t="n">
-        <v>11039043240</v>
+        <v>69264692475</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>31200</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>21000</v>
       </c>
       <c r="R19" t="n">
-        <v>33000</v>
+        <v>481000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '로봇']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10290</v>
+        <v>10230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="H20" t="n">
         <v>5.75</v>
@@ -2266,7 +2266,7 @@
         <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>18975353870</v>
+        <v>19164156865</v>
       </c>
       <c r="P20" t="n">
         <v>15640</v>
@@ -2275,7 +2275,7 @@
         <v>5470</v>
       </c>
       <c r="R20" t="n">
-        <v>-85000</v>
+        <v>-120000</v>
       </c>
       <c r="S20" t="n">
         <v>-2000</v>
@@ -2326,13 +2326,13 @@
         <v>0.42</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
         <v>4.81</v>
@@ -2358,7 +2358,7 @@
         <v>4.39</v>
       </c>
       <c r="O21" t="n">
-        <v>16720291895</v>
+        <v>16794965110</v>
       </c>
       <c r="P21" t="n">
         <v>10480</v>
@@ -2367,7 +2367,7 @@
         <v>3150</v>
       </c>
       <c r="R21" t="n">
-        <v>-336000</v>
+        <v>-432000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5410</v>
+        <v>5420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.75%</t>
+          <t>-5.57%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3601832550</v>
+        <v>3627191580</v>
       </c>
       <c r="P22" t="n">
         <v>9680</v>
@@ -2459,23 +2459,23 @@
         <v>371</v>
       </c>
       <c r="R22" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 뉴스가 연이어 발생하며 하한가 우려가 제기되었으나, 일부에서는 보합 가능성 및 악재 노출 완료 언급.</t>
+          <t>본느, 반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 투심 훼손. 주가 하락 가능성 및 불확실성 증대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '매각']</t>
+          <t>['반기보고서', '악재', '투심']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20260907_13.xlsx
+++ b/data/trending_integrated_20260907_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>799</v>
+        <v>559</v>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="G2" t="n">
-        <v>1223</v>
+        <v>783</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>776552268475</v>
+        <v>776910283925</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스카이랩스, 거래량 증가와 함께 급등 가능성 언급. '주포' 언급 등 시세 조종 관련 논란 존재.</t>
+          <t>주포 언급 및 거래량 증가에 따른 급등 기대. F1 재무 투자자 상장일 미매도 소식.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['거래량', '시세 조종', '주포']</t>
+          <t>['주포', '거래량', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10220</v>
+        <v>10270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.40%</t>
+          <t>+22.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>118262341050</v>
+        <v>121551260410</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9970</v>
+        <v>18940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.88%</t>
+          <t>+20.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8180</v>
+        <v>15750</v>
       </c>
       <c r="K4" t="n">
-        <v>8200</v>
+        <v>16080</v>
       </c>
       <c r="L4" t="n">
-        <v>10390</v>
+        <v>19110</v>
       </c>
       <c r="M4" t="n">
-        <v>8120</v>
+        <v>15920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>75434428540</v>
+        <v>83129209455</v>
       </c>
       <c r="P4" t="n">
-        <v>22500</v>
+        <v>34650</v>
       </c>
       <c r="Q4" t="n">
-        <v>4560</v>
+        <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>152000</v>
+        <v>-36000</v>
       </c>
       <c r="S4" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>매드업, AI 관련주로 부각되며 외국인·프로그램 매수세 유입. 매물대 소화 후 상승 기대감 형성.</t>
+          <t>저평가 기업 분석 및 텐배거 기대. 공모가 대비 현재 가격 비교 및 저항대 소화.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '외국인 매수', '매물대']</t>
+          <t>['공모가', '저평가', '텐배거']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0039P0</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51800</v>
+        <v>9820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+20.05%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="E5" t="n">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>606</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
-        <v>14.18</v>
+        <v>1.58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43850</v>
+        <v>8180</v>
       </c>
       <c r="K5" t="n">
-        <v>45650</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>55000</v>
+        <v>10390</v>
       </c>
       <c r="M5" t="n">
-        <v>45650</v>
+        <v>8120</v>
       </c>
       <c r="N5" t="n">
-        <v>13.71</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>140581808925</v>
+        <v>78758810440</v>
       </c>
       <c r="P5" t="n">
-        <v>108900</v>
+        <v>22500</v>
       </c>
       <c r="Q5" t="n">
-        <v>18230</v>
+        <v>4560</v>
       </c>
       <c r="R5" t="n">
-        <v>156000</v>
+        <v>152000</v>
       </c>
       <c r="S5" t="n">
-        <v>-11000</v>
+        <v>-9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
+          <t>외인/프로그램 매수세 유입 감지. AI 셀럽 영상 매출 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '매물벽', '수주 공시']</t>
+          <t>['AI', '프로그램매수', '매물대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>0039P0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>50800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.57%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>610</v>
       </c>
       <c r="H6" t="n">
-        <v>1.08</v>
+        <v>14.18</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>15750</v>
+        <v>43850</v>
       </c>
       <c r="K6" t="n">
-        <v>16080</v>
+        <v>45650</v>
       </c>
       <c r="L6" t="n">
-        <v>18900</v>
+        <v>55000</v>
       </c>
       <c r="M6" t="n">
-        <v>15920</v>
+        <v>45650</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>13.71</v>
       </c>
       <c r="O6" t="n">
-        <v>74204682845</v>
+        <v>143386644525</v>
       </c>
       <c r="P6" t="n">
-        <v>34650</v>
+        <v>108900</v>
       </c>
       <c r="Q6" t="n">
-        <v>6980</v>
+        <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>-36000</v>
+        <v>156000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>레메디, 저평가된 기업으로 텐배거 기대감 존재. 저항대 소화 및 반도체 섹터 흐름에 따른 추가 상승 가능성.</t>
+          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '텐배거', '반도체']</t>
+          <t>['공매도', '매물벽', '수주 공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.41%</t>
+          <t>+10.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>184414286932</v>
+        <v>186427769594</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
+          <t>단기 수익 달성 후 투자주의 필요성 제기. 탈모 관련 사업 반복 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자주의', '탈모', '프로그램 매매']</t>
+          <t>['탈모', '수익', '투자주의']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86700</v>
+        <v>86600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.47%</t>
+          <t>+9.34%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F8" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G8" t="n">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>309901135300</v>
+        <v>323876864300</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 일론 머스크 관련 뉴스 및 대규모 투자 발표로 인한 기대감 급증. 하반기 수주 전망 긍정적.</t>
+          <t>일론 머스크의 두산에너빌리티 선택 속보. 하반기 본격 수주 기대 및 기술력 입증.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['일론 머스크', '가스터빈', '수주']</t>
+          <t>['가스터빈', '대미투자', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H9" t="n">
         <v>1.61</v>
@@ -1254,7 +1254,7 @@
         <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>15032602260</v>
+        <v>15296274690</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1757000</v>
+        <v>1766000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+7.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>797</v>
+        <v>637</v>
       </c>
       <c r="F10" t="n">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="G10" t="n">
-        <v>2633</v>
+        <v>2161</v>
       </c>
       <c r="H10" t="n">
         <v>50.5</v>
@@ -1337,7 +1337,7 @@
         <v>1737000</v>
       </c>
       <c r="L10" t="n">
-        <v>1758000</v>
+        <v>1768000</v>
       </c>
       <c r="M10" t="n">
         <v>1733000</v>
@@ -1346,7 +1346,7 @@
         <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3441858171500</v>
+        <v>3633699737000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 메모리 재고 감소 및 외국인·기관 매수세 증가로 인한 상승 추세 가속. 200달성 기대감 고조.</t>
+          <t>메모리 재고 감소 전망 속 2차 상승 시작 기대. 외인/기관 매수 확대 및 개인 매도세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '재고', '외국인 매수']</t>
+          <t>['메모리', '재고', '상승 추세']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F11" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G11" t="n">
-        <v>1293</v>
+        <v>1316</v>
       </c>
       <c r="H11" t="n">
         <v>29.46</v>
@@ -1438,7 +1438,7 @@
         <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>304727357250</v>
+        <v>309267583500</v>
       </c>
       <c r="P11" t="n">
         <v>438000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
+          <t>LG전자 로봇 관련 기술력 부각 및 목표주가 100만원 제시. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2026', '모터 기술']</t>
+          <t>['로봇', '모터 기술', '목표주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17850</v>
+        <v>17730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.93%</t>
+          <t>+5.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>93629367575</v>
+        <v>96836919485</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1596,7 +1596,7 @@
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H13" t="n">
         <v>0.6</v>
@@ -1622,7 +1622,7 @@
         <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>93728011260</v>
+        <v>94122052565</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>267750</v>
+        <v>268000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.79%</t>
+          <t>+4.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F14" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G14" t="n">
-        <v>1877</v>
+        <v>1926</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1705,7 +1705,7 @@
         <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>268000</v>
+        <v>268500</v>
       </c>
       <c r="M14" t="n">
         <v>264000</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2349215087750</v>
+        <v>2589704910000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성전자, 반도체 재고 감소 및 HBM 가격 상승 기대감 형성. 그러나 정치적 언급과 불확실한 전망이 혼재.</t>
+          <t>미국장 휴장 속 재고 바닥 전망 및 기술적 반등 기대. 외국인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HBM', '재고', '반도체']</t>
+          <t>['HBM', '반도체', '영업이익']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13460</v>
+        <v>13400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1800,13 +1800,13 @@
         <v>14100</v>
       </c>
       <c r="M15" t="n">
-        <v>13400</v>
+        <v>13360</v>
       </c>
       <c r="N15" t="n">
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>68873394290</v>
+        <v>70636470665</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6750</v>
+        <v>6770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
         <v>16.4</v>
@@ -1898,7 +1898,7 @@
         <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>11088297960</v>
+        <v>11180149305</v>
       </c>
       <c r="P16" t="n">
         <v>13000</v>
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22550</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>48.95</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>22500</v>
+        <v>30200</v>
       </c>
       <c r="K17" t="n">
-        <v>23100</v>
+        <v>30350</v>
       </c>
       <c r="L17" t="n">
-        <v>24000</v>
+        <v>30900</v>
       </c>
       <c r="M17" t="n">
-        <v>21500</v>
+        <v>29900</v>
       </c>
       <c r="N17" t="n">
-        <v>4.98</v>
+        <v>24.02</v>
       </c>
       <c r="O17" t="n">
-        <v>127257326225</v>
+        <v>70538324725</v>
       </c>
       <c r="P17" t="n">
-        <v>50600</v>
+        <v>31200</v>
       </c>
       <c r="Q17" t="n">
-        <v>9070</v>
+        <v>21000</v>
       </c>
       <c r="R17" t="n">
-        <v>9000</v>
+        <v>481000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>113000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16120</v>
+        <v>16140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
         <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>38839397945</v>
+        <v>39379321330</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30250</v>
+        <v>22400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="H19" t="n">
-        <v>48.95</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>30200</v>
+        <v>22500</v>
       </c>
       <c r="K19" t="n">
-        <v>30350</v>
+        <v>23100</v>
       </c>
       <c r="L19" t="n">
-        <v>30900</v>
+        <v>24000</v>
       </c>
       <c r="M19" t="n">
-        <v>29900</v>
+        <v>21500</v>
       </c>
       <c r="N19" t="n">
-        <v>24.02</v>
+        <v>4.98</v>
       </c>
       <c r="O19" t="n">
-        <v>69264692475</v>
+        <v>128704847300</v>
       </c>
       <c r="P19" t="n">
-        <v>31200</v>
+        <v>50600</v>
       </c>
       <c r="Q19" t="n">
-        <v>21000</v>
+        <v>9070</v>
       </c>
       <c r="R19" t="n">
-        <v>481000</v>
+        <v>9000</v>
       </c>
       <c r="S19" t="n">
-        <v>113000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H20" t="n">
         <v>5.75</v>
@@ -2266,7 +2266,7 @@
         <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>19164156865</v>
+        <v>19311642465</v>
       </c>
       <c r="P20" t="n">
         <v>15640</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5450</v>
+        <v>5470</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.42</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H21" t="n">
         <v>4.81</v>
@@ -2358,7 +2358,7 @@
         <v>4.39</v>
       </c>
       <c r="O21" t="n">
-        <v>16794965110</v>
+        <v>17047380650</v>
       </c>
       <c r="P21" t="n">
         <v>10480</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5420</v>
+        <v>5390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-6.10%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3627191580</v>
+        <v>3683674400</v>
       </c>
       <c r="P22" t="n">
         <v>9680</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>본느, 반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 투심 훼손. 주가 하락 가능성 및 불확실성 증대.</t>
+          <t>악재 뉴스 발생(조선비즈 기사) 및 투심 훼손 우려. 반기보고서 제출 지연.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '투심']</t>
+          <t>['악재', '반기보고서', '투심']</t>
         </is>
       </c>
       <c r="X22" t="n">
